--- a/data-raw/bmw_benchmarks_2025.xlsx
+++ b/data-raw/bmw_benchmarks_2025.xlsx
@@ -10,12 +10,14 @@
     <sheet name="bmw_female" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="bmw_aapi" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="bmw_zm" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="bmw_millennial" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="bmw_genz" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve">svy_q</t>
   </si>
@@ -171,6 +173,15 @@
   </si>
   <si>
     <t xml:space="preserve">Gen Z/Millennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen Z</t>
   </si>
 </sst>
 </file>
@@ -3829,4 +3840,1728 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.594747918382286</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10929</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.940616707841383</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10280</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10929</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.567412451361866</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5833</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.577334630350193</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5935</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.424805447470816</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4367</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.66099221789883</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6795</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.481517509727625</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4950</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.364202334630349</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3744</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.315077821011672</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3239</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.628404669260698</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6460</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.481614785992216</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4951</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.555252918287936</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5708</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.485992217898831</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4996</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.506712062256808</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5209</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.428793774319065</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4408</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.506420233463033</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5206</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.611964980544745</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6291</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.51293774319066</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5273</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.446400778210115</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4589</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.575583657587547</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5917</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.493968871595329</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5078</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.551264591439687</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.521206225680932</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5358</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.597178988326846</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6139</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.580155642023344</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5964</v>
+      </c>
+      <c r="E26" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.485505836575874</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4991</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.542412451361866</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5576</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.533171206225679</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5481</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.378696498054473</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3893</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.604766536964979</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6217</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.503793774319064</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5179</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.585603112840465</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6020</v>
+      </c>
+      <c r="E33" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.617801556420231</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6351</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.578988326848247</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5952</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.642217898832683</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6602</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.431614785992216</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4437</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10280</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.465643762508334</v>
+      </c>
+      <c r="D2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.903268845897286</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1354</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.564254062038407</v>
+      </c>
+      <c r="D4" t="n">
+        <v>764</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.604874446085677</v>
+      </c>
+      <c r="D5" t="n">
+        <v>819</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.475627769571638</v>
+      </c>
+      <c r="D6" t="n">
+        <v>644</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.655834564254071</v>
+      </c>
+      <c r="D7" t="n">
+        <v>888</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.486706056129983</v>
+      </c>
+      <c r="D8" t="n">
+        <v>659</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.351550960118167</v>
+      </c>
+      <c r="D9" t="n">
+        <v>476</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.301329394387</v>
+      </c>
+      <c r="D10" t="n">
+        <v>408</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.608567208271793</v>
+      </c>
+      <c r="D11" t="n">
+        <v>824</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.50295420974889</v>
+      </c>
+      <c r="D12" t="n">
+        <v>681</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.544313146233383</v>
+      </c>
+      <c r="D13" t="n">
+        <v>737</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.49335302806499</v>
+      </c>
+      <c r="D14" t="n">
+        <v>668</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.516248153618906</v>
+      </c>
+      <c r="D15" t="n">
+        <v>699</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.442392909896601</v>
+      </c>
+      <c r="D16" t="n">
+        <v>599</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.497784342688329</v>
+      </c>
+      <c r="D17" t="n">
+        <v>674</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.593057607090108</v>
+      </c>
+      <c r="D18" t="n">
+        <v>803</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.489660265878875</v>
+      </c>
+      <c r="D19" t="n">
+        <v>663</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.480797636632199</v>
+      </c>
+      <c r="D20" t="n">
+        <v>651</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.565731166912853</v>
+      </c>
+      <c r="D21" t="n">
+        <v>766</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.499261447562775</v>
+      </c>
+      <c r="D22" t="n">
+        <v>676</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.518463810930575</v>
+      </c>
+      <c r="D23" t="n">
+        <v>702</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.491875923190544</v>
+      </c>
+      <c r="D24" t="n">
+        <v>666</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.557607090103399</v>
+      </c>
+      <c r="D25" t="n">
+        <v>755</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.554652880354507</v>
+      </c>
+      <c r="D26" t="n">
+        <v>751</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.476366322008861</v>
+      </c>
+      <c r="D27" t="n">
+        <v>645</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.507385524372229</v>
+      </c>
+      <c r="D28" t="n">
+        <v>687</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.497784342688329</v>
+      </c>
+      <c r="D29" t="n">
+        <v>674</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.350812407680944</v>
+      </c>
+      <c r="D30" t="n">
+        <v>475</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.581979320531761</v>
+      </c>
+      <c r="D31" t="n">
+        <v>788</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.49556868537666</v>
+      </c>
+      <c r="D32" t="n">
+        <v>671</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F32" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.567208271787299</v>
+      </c>
+      <c r="D33" t="n">
+        <v>768</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.604135893648454</v>
+      </c>
+      <c r="D34" t="n">
+        <v>818</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.520679468242244</v>
+      </c>
+      <c r="D35" t="n">
+        <v>705</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.604874446085677</v>
+      </c>
+      <c r="D36" t="n">
+        <v>819</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.432053175775478</v>
+      </c>
+      <c r="D37" t="n">
+        <v>585</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1354</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>